--- a/OrderbookAutomation/output/Workbook_Profile.xlsx
+++ b/OrderbookAutomation/output/Workbook_Profile.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,17 +467,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E2" t="n">
-        <v>7312</v>
+        <v>7179</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -726,36 +726,6 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>37</v>
-      </c>
-      <c r="E11" t="n">
-        <v>6514</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -770,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G219"/>
+  <dimension ref="A1:G189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,28 +788,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sales Order Qty</t>
+          <t>Sales Order No.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>3612003019</t>
         </is>
       </c>
     </row>
@@ -851,28 +821,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sales Qty MTD</t>
+          <t>Item No.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -884,17 +854,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Forecast Qty</t>
+          <t>Matl.Code</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -905,7 +875,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3011973</t>
         </is>
       </c>
     </row>
@@ -917,12 +887,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sold-to party</t>
+          <t>NDC Code</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -934,11 +904,11 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9700378</t>
+          <t>64380018701</t>
         </is>
       </c>
     </row>
@@ -950,12 +920,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sold-to party Name</t>
+          <t>Material Description</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -967,11 +937,11 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>KROGER</t>
+          <t>ZAFIRLUKAST TABS 10MG 60</t>
         </is>
       </c>
     </row>
@@ -983,28 +953,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>S.O. Type</t>
+          <t>Total Stock In-hand</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ZTRU</t>
+          <t>19512</t>
         </is>
       </c>
     </row>
@@ -1016,28 +986,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Unit Price</t>
+          <t>PackSize(MOQ)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1049,28 +1019,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sales Value (FC)</t>
+          <t>Sales Order Qty</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>196.56</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1052,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WAC/BG price in EDI</t>
+          <t>Sales Qty MTD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1103,7 +1073,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>168</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1085,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PO number</t>
+          <t>Forecast Qty</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1132,11 +1102,11 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>21918</t>
+          <t>122</t>
         </is>
       </c>
     </row>
@@ -1148,17 +1118,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PO date</t>
+          <t>Sold-to party</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1169,7 +1139,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7/30/26</t>
+          <t>9700378</t>
         </is>
       </c>
     </row>
@@ -1181,28 +1151,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ship-to party</t>
+          <t>Sold-to party Name</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9800166</t>
+          <t>KROGER</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1184,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ship-to party Name</t>
+          <t>S.O. Type</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1231,11 +1201,11 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>KROGER_BLUFFTON</t>
+          <t>ZTRU</t>
         </is>
       </c>
     </row>
@@ -1247,28 +1217,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Unit Price</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1111 SOUTH ADAMS STREET</t>
+          <t>8.19</t>
         </is>
       </c>
     </row>
@@ -1280,28 +1250,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Sales Value (FC)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>BLUFFTON</t>
+          <t>196.56</t>
         </is>
       </c>
     </row>
@@ -1313,28 +1283,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>WAC/BG price in EDI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>8.19</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1316,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Postal Code</t>
+          <t>PO number</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1363,11 +1333,11 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>46714</t>
+          <t>21918</t>
         </is>
       </c>
     </row>
@@ -1379,17 +1349,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>PO date</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>datetime64[us]</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1400,7 +1370,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>2026-07-30 00:00:00</t>
         </is>
       </c>
     </row>
@@ -1412,28 +1382,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Reas. Rej.</t>
+          <t>Ship-to party</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Y6</t>
+          <t>9800166</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1415,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Reason for Rejection</t>
+          <t>Ship-to party Name</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1462,11 +1432,11 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ZUS Y6 Block</t>
+          <t>KROGER_BLUFFTON</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1448,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Material Blk</t>
+          <t>Street</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1495,11 +1465,11 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1111 SOUTH ADAMS STREET</t>
         </is>
       </c>
     </row>
@@ -1511,26 +1481,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Floor limit Blk</t>
+          <t>City</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>BLUFFTON</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1540,26 +1514,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Multiple of MOQ Blk</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1569,26 +1547,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Expected Price Blk</t>
+          <t>Postal Code</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>46714</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1598,12 +1580,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DEA Number (Customer Master)</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1615,11 +1597,11 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PP0220828</t>
+          <t>US</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1613,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Req. Delivery Date</t>
+          <t>Reas. Rej.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1652,7 +1634,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8/6/26</t>
+          <t>Y6</t>
         </is>
       </c>
     </row>
@@ -1664,262 +1646,250 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SOM Indc.</t>
+          <t>Reason for Rejection</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ZUS Y6 Block</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mat_Desc,_MOQ_,_Material_#.xlsx</t>
+          <t>raw_OB.xlsx</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HANA Material</t>
+          <t>Material Blk</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3011903</t>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mat_Desc,_MOQ_,_Material_#.xlsx</t>
+          <t>raw_OB.xlsx</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NDC code</t>
+          <t>Floor limit Blk</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>64380020101</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mat_Desc,_MOQ_,_Material_#.xlsx</t>
+          <t>raw_OB.xlsx</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Material Description</t>
+          <t>Multiple of MOQ Blk</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>AMLO/HCTZ/VALSAR TAB 10/25/320 MG 30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mat_Desc,_MOQ_,_Material_#.xlsx</t>
+          <t>raw_OB.xlsx</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOQ </t>
+          <t>Expected Price Blk</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07-30_inv.xlsx</t>
+          <t>raw_OB.xlsx</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NDC</t>
+          <t>DEA Number (Customer Master)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>64380016101</t>
+          <t>PP0220828</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07-30_inv.xlsx</t>
+          <t>raw_OB.xlsx</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>Req. Delivery Date</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>datetime64[us]</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>64380-161-01</t>
+          <t>2026-08-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07-30_inv.xlsx</t>
+          <t>raw_OB.xlsx</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>UOB</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>SOM Indc.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Valganciclovir Tablets 450mg 60ct</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07-30_inv.xlsx</t>
+          <t>Mat_Desc,_MOQ_,_Material_#.xlsx</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1929,30 +1899,30 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lot</t>
+          <t>HANA Material</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>7262830A</t>
+          <t>3011903</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07-30_inv.xlsx</t>
+          <t>Mat_Desc,_MOQ_,_Material_#.xlsx</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1962,7 +1932,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Expiration Date</t>
+          <t>NDC code</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1974,18 +1944,18 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>46507</t>
+          <t>64380020101</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07-30_inv.xlsx</t>
+          <t>Mat_Desc,_MOQ_,_Material_#.xlsx</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1995,7 +1965,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hold Codes</t>
+          <t>Material Description</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2004,21 +1974,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SD,HD</t>
+          <t>AMLO/HCTZ/VALSAR TAB 10/25/320 MG 30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07-30_inv.xlsx</t>
+          <t>Mat_Desc,_MOQ_,_Material_#.xlsx</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2028,21 +1998,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Product Status</t>
+          <t xml:space="preserve">MOQ </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2057,7 +2031,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Actual Quantity</t>
+          <t>NDC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2069,11 +2043,11 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>64380016101</t>
         </is>
       </c>
     </row>
@@ -2090,23 +2064,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Allocated Quantity</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64380-161-01</t>
         </is>
       </c>
     </row>
@@ -2123,23 +2097,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Valganciclovir Tablets 450mg 60ct</t>
         </is>
       </c>
     </row>
@@ -2156,23 +2130,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>On Hand Damaged</t>
+          <t>Lot</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7262830A</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2163,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>On Hand Hold</t>
+          <t>Expiration Date</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2201,11 +2175,11 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>46507</t>
         </is>
       </c>
     </row>
@@ -2222,30 +2196,30 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>On Hand Misc</t>
+          <t>Hold Codes</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>SD,HD</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Open_Order_Summary.xlsx</t>
+          <t>07-30_inv.xlsx</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2255,7 +2229,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Create Date</t>
+          <t>Product Status</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2267,18 +2241,14 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>7/24/26</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Open_Order_Summary.xlsx</t>
+          <t>07-30_inv.xlsx</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2288,30 +2258,30 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PH_ORD_DATE</t>
+          <t>Actual Quantity</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>7/24/26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Open_Order_Summary.xlsx</t>
+          <t>07-30_inv.xlsx</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2321,12 +2291,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Current Date</t>
+          <t>Allocated Quantity</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2337,14 +2307,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>7/30/26</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Open_Order_Summary.xlsx</t>
+          <t>07-30_inv.xlsx</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2354,7 +2324,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>No of days</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2366,18 +2336,18 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Open_Order_Summary.xlsx</t>
+          <t>07-30_inv.xlsx</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2387,30 +2357,30 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>On Hand Damaged</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>&gt;4 days</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Open_Order_Summary.xlsx</t>
+          <t>07-30_inv.xlsx</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2420,7 +2390,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PH_PKT_CTRL_NBR</t>
+          <t>On Hand Hold</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2432,18 +2402,18 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8061682605</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Open_Order_Summary.xlsx</t>
+          <t>07-30_inv.xlsx</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2453,7 +2423,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Uniq ID</t>
+          <t>On Hand Misc</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2465,11 +2435,11 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1100005792</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2486,23 +2456,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SO#</t>
+          <t>Create Date</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>3612002867</t>
+          <t>7/24/26</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2489,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PO#</t>
+          <t>PH_ORD_DATE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2531,11 +2501,11 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C7188832NLC</t>
+          <t>7/24/26</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2522,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pickticket Status</t>
+          <t>Current Date</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2564,11 +2534,11 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>In Picking</t>
+          <t>7/30/26</t>
         </is>
       </c>
     </row>
@@ -2585,12 +2555,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>No of days</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2601,7 +2571,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>64380-201-01</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IM_SKU_DESC</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2634,7 +2604,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Amlo/Hctz/Valsar Tab 10/25/320 Mg 30</t>
+          <t>&gt;4 days</t>
         </is>
       </c>
     </row>
@@ -2651,23 +2621,23 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SPI/CR</t>
+          <t>PH_PKT_CTRL_NBR</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>8061682605</t>
         </is>
       </c>
     </row>
@@ -2684,23 +2654,23 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Uniq ID</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>64380-201-01Cardinal</t>
+          <t>1100005792</t>
         </is>
       </c>
     </row>
@@ -2717,23 +2687,23 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PH_SOLDTO_NAME</t>
+          <t>SO#</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>CAH GLOBAL CONTRACTING COMPANY LTD</t>
+          <t>3612002867</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2720,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Customer Group</t>
+          <t>PO#</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2762,11 +2732,11 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cardinal</t>
+          <t>C7188832NLC</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2753,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Street Address</t>
+          <t>Pickticket Status</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2795,11 +2765,11 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>5995 COMMERCE CENTER DRIVE</t>
+          <t>In Picking</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2786,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2828,11 +2798,11 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>GROVEPORT</t>
+          <t>64380-201-01</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2819,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PH_SHIPTO_STATE</t>
+          <t>IM_SKU_DESC</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2861,11 +2831,11 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>Amlo/Hctz/Valsar Tab 10/25/320 Mg 30</t>
         </is>
       </c>
     </row>
@@ -2882,23 +2852,23 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Total </t>
+          <t>SPI/CR</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>CR</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2885,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2927,18 +2897,18 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>BRB</t>
+          <t>64380-201-01Cardinal</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Buying_groups.xlsx</t>
+          <t>Open_Order_Summary.xlsx</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2948,7 +2918,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>PH_SOLDTO_NAME</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2960,18 +2930,18 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>American Health Packaging</t>
+          <t>CAH GLOBAL CONTRACTING COMPANY LTD</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Buying_groups.xlsx</t>
+          <t>Open_Order_Summary.xlsx</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2981,7 +2951,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Customer buying group</t>
+          <t>Customer Group</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2997,14 +2967,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>AHP</t>
+          <t>Cardinal</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Awards.xlsx</t>
+          <t>Open_Order_Summary.xlsx</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3014,7 +2984,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lookup</t>
+          <t>Street Address</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3026,18 +2996,18 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>129</v>
+        <v>4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>64380072701CAH GLOBAL CONTRACTING COMPANY LTD</t>
+          <t>5995 COMMERCE CENTER DRIVE</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Awards.xlsx</t>
+          <t>Open_Order_Summary.xlsx</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3047,30 +3017,30 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NDC</t>
+          <t>City</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>64380072701</t>
+          <t>GROVEPORT</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Awards.xlsx</t>
+          <t>Open_Order_Summary.xlsx</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3080,7 +3050,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>PH_SHIPTO_STATE</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3096,14 +3066,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gaba Tabs</t>
+          <t>OH</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Awards.xlsx</t>
+          <t>Open_Order_Summary.xlsx</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3113,30 +3083,30 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t xml:space="preserve"> Total </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gabapentin Tablets 600Mg 100Ct</t>
+          <t>624</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Awards.xlsx</t>
+          <t>Open_Order_Summary.xlsx</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3146,7 +3116,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3158,18 +3128,18 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>BRB</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Awards.xlsx</t>
+          <t>Buying_groups.xlsx</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3179,7 +3149,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Award Type</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3188,21 +3158,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Backup</t>
+          <t>American Health Packaging</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Awards.xlsx</t>
+          <t>Buying_groups.xlsx</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3212,7 +3182,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sold to party</t>
+          <t>Customer buying group</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3224,18 +3194,18 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>CAH GLOBAL CONTRACTING COMPANY LTD</t>
+          <t>AHP</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CIP.xlsx</t>
+          <t>Awards.xlsx</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3245,30 +3215,30 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NDC</t>
+          <t>Lookup</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>64380016001</t>
+          <t>64380072701CAH GLOBAL CONTRACTING COMPANY LTD</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CIP.xlsx</t>
+          <t>Awards.xlsx</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3278,30 +3248,30 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>NDC</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Megestrol Acetate OS 40mg/mL, 240</t>
+          <t>64380072701</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CIP.xlsx</t>
+          <t>Awards.xlsx</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3311,7 +3281,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3323,18 +3293,18 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>36K wk of 08/17</t>
+          <t>Gaba Tabs</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CIP.xlsx</t>
+          <t>Awards.xlsx</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3344,7 +3314,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Customer ETA</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3356,18 +3326,18 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>wk 8/17</t>
+          <t>Gabapentin Tablets 600Mg 100Ct</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Awards.xlsx</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3377,30 +3347,30 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sales Order No.</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>3612002936</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Awards.xlsx</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3410,30 +3380,30 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Item No.</t>
+          <t>Award Type</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Backup</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Awards.xlsx</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3443,7 +3413,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lookup</t>
+          <t>Sold to party</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3455,362 +3425,362 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>64380020101EXPRESS SCRIPTS</t>
+          <t>CAH GLOBAL CONTRACTING COMPANY LTD</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>CIP.xlsx</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>10</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>64380016001</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CIP.xlsx</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>10</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Megestrol Acetate OS 40mg/mL, 240</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CIP.xlsx</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>10</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>36K wk of 08/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CIP.xlsx</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Customer ETA</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>6</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>wk 8/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>sales_summ.xlsx</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Sales Order No.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>3612002936</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>sales_summ.xlsx</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>sales_summ.xlsx</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>64380020101EXPRESS SCRIPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>sales_summ.xlsx</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
         <is>
           <t>Matl._x000d_
 Code</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>int64</t>
         </is>
       </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="n">
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
         <v>1</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>3011903</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>sales_summ.xlsx</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
         <is>
           <t>NDC Code</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>int64</t>
         </is>
       </c>
-      <c r="E84" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" t="n">
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
         <v>1</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>64380020101</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>sales_summ.xlsx</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
         <is>
           <t>Material Description</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
         <v>1</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>AMLO/HCTZ/VALSAR TAB 10/25/320 MG 30</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>sales_summ.xlsx</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
         <is>
           <t>Total Stock _x000d_
 In-hand</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>23,061</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>sales_summ.xlsx</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>UPS Inventory</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>21,696</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>sales_summ.xlsx</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Pack Size (MOQ)</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>int64</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>sales_summ.xlsx</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Sales Order Qty</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>int64</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>sales_summ.xlsx</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Sales Qty MTD</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>int64</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>sales_summ.xlsx</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Forecast Qty</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>int64</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>sales_summ.xlsx</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Sold-to party</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>int64</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>9700306</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>sales_summ.xlsx</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Sold-to party Name</t>
-        </is>
-      </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>str</t>
@@ -3824,7 +3794,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>EXPRESS SCRIPTS</t>
+          <t>23,061</t>
         </is>
       </c>
     </row>
@@ -3841,21 +3811,25 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>UPS Inventory</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
         <v>1</v>
       </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>21,696</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3870,12 +3844,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>S.O. Type</t>
+          <t>Pack Size (MOQ)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -3886,7 +3860,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ZTRU</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -3903,12 +3877,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Unit Price </t>
+          <t>Sales Order Qty</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -3919,7 +3893,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>160.06</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -3936,12 +3910,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sales Value (FC) </t>
+          <t>Sales Qty MTD</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -3952,7 +3926,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>11,524.32</t>
+          <t>432</t>
         </is>
       </c>
     </row>
@@ -3969,12 +3943,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>WAC/BG price in EDI</t>
+          <t>Forecast Qty</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -3985,7 +3959,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>160.06</t>
+          <t>366</t>
         </is>
       </c>
     </row>
@@ -4002,12 +3976,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PO Number</t>
+          <t>Sold-to party</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -4018,7 +3992,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>1036729-2331</t>
+          <t>9700306</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4009,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PO Date</t>
+          <t>Sold-to party Name</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4051,7 +4025,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>7/28/26</t>
+          <t>EXPRESS SCRIPTS</t>
         </is>
       </c>
     </row>
@@ -4068,25 +4042,21 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ship-to party</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>9800112</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4101,7 +4071,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ship-to party Name</t>
+          <t>S.O. Type</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4117,7 +4087,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>EXPRESS SCRIPTS_BURLINGTON</t>
+          <t>ZTRU</t>
         </is>
       </c>
     </row>
@@ -4134,12 +4104,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t xml:space="preserve"> Unit Price </t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -4150,7 +4120,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2040 ROUTE 130 NORTH</t>
+          <t>160.06</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4137,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>City</t>
+          <t xml:space="preserve"> Sales Value (FC) </t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4183,7 +4153,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>BURLINGTON</t>
+          <t>11,524.32</t>
         </is>
       </c>
     </row>
@@ -4200,12 +4170,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>WAC/BG price in EDI</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -4216,7 +4186,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>160.06</t>
         </is>
       </c>
     </row>
@@ -4233,12 +4203,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Postal Code</t>
+          <t>PO Number</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -4249,7 +4219,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>1036729-2331</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4236,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>PO Date</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4282,7 +4252,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>7/28/26</t>
         </is>
       </c>
     </row>
@@ -4299,12 +4269,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Reas. Rej.</t>
+          <t>Ship-to party</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -4315,7 +4285,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Y6</t>
+          <t>9800112</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4302,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Reason for Rejection</t>
+          <t>Ship-to party Name</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4348,7 +4318,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>ZUS Y6 Block</t>
+          <t>EXPRESS SCRIPTS_BURLINGTON</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4335,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Material Blk</t>
+          <t>Street</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4381,7 +4351,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>2040 ROUTE 130 NORTH</t>
         </is>
       </c>
     </row>
@@ -4398,21 +4368,25 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Floor limit Blk</t>
+          <t>City</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
         <v>1</v>
       </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>BURLINGTON</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4427,21 +4401,25 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Multiple of MOQ Blk</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
         <v>1</v>
       </c>
-      <c r="F112" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4456,21 +4434,25 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Expected Price Blk</t>
+          <t>Postal Code</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
         <v>1</v>
       </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>8016</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4485,7 +4467,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>DEA Number (Customer Master)</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4501,7 +4483,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>FE4492738</t>
+          <t>US</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4500,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Req. Delivery Date</t>
+          <t>Reas. Rej.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4534,7 +4516,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>7/28/26</t>
+          <t>Y6</t>
         </is>
       </c>
     </row>
@@ -4551,26 +4533,30 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SOM Indc.</t>
+          <t>Reason for Rejection</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
         <v>1</v>
       </c>
-      <c r="F116" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>ZUS Y6 Block</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Strend.xlsx</t>
+          <t>sales_summ.xlsx</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4580,30 +4566,30 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NDC Code</t>
+          <t>Material Blk</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E117" t="n">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>64380020101</t>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Strend.xlsx</t>
+          <t>sales_summ.xlsx</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4613,30 +4599,26 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Material Description</t>
+          <t>Floor limit Blk</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>4</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>AMLO/HCTZ/VALSAR TAB 10/25/320 MG 30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Strend.xlsx</t>
+          <t>sales_summ.xlsx</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4646,30 +4628,26 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Multiple of MOQ Blk</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>4</v>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>AVH</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Strend.xlsx</t>
+          <t>sales_summ.xlsx</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4679,30 +4657,26 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t>Expected Price Blk</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>2</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Strend.xlsx</t>
+          <t>sales_summ.xlsx</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4712,7 +4686,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SPI/CR</t>
+          <t>DEA Number (Customer Master)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4724,18 +4698,18 @@
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>FE4492738</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Strend.xlsx</t>
+          <t>sales_summ.xlsx</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4745,7 +4719,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sold-to party Name</t>
+          <t>Req. Delivery Date</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4757,18 +4731,18 @@
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>CENCORA GLOBAL PROCUREMENT</t>
+          <t>7/28/26</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Strend.xlsx</t>
+          <t>sales_summ.xlsx</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4778,25 +4752,21 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cust Group</t>
+          <t>SOM Indc.</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>23</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>WBAD</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4811,23 +4781,23 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Cont ID </t>
+          <t>NDC Code</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E124" t="n">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>ABCS0614</t>
+          <t>64380020101</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4814,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Material Description</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4856,11 +4826,11 @@
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>64380020101CENCORA GLOBAL PROCUREMENT</t>
+          <t>AMLO/HCTZ/VALSAR TAB 10/25/320 MG 30</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4847,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jul-22 </t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4886,14 +4856,14 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> -   </t>
+          <t>AVH</t>
         </is>
       </c>
     </row>
@@ -4910,23 +4880,23 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Aug-22 </t>
+          <t>Count</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 336 </t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4913,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sep-22 </t>
+          <t>SPI/CR</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4952,14 +4922,14 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,056 </t>
+          <t>CR</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4946,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Oct-22 </t>
+          <t>Sold-to party Name</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4985,14 +4955,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 696 </t>
+          <t>CENCORA GLOBAL PROCUREMENT</t>
         </is>
       </c>
     </row>
@@ -5009,7 +4979,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Nov-22 </t>
+          <t>Cust Group</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5018,14 +4988,14 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 360 </t>
+          <t>WBAD</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5012,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dec-22 </t>
+          <t xml:space="preserve"> Cont ID </t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5051,14 +5021,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 864 </t>
+          <t>ABCS0614</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5045,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jan-23 </t>
+          <t>x</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5084,14 +5054,14 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,104 </t>
+          <t>64380020101CENCORA GLOBAL PROCUREMENT</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5078,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feb-23 </t>
+          <t xml:space="preserve"> Jul-22 </t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5120,11 +5090,11 @@
         <v>45</v>
       </c>
       <c r="F133" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,152 </t>
+          <t xml:space="preserve"> -   </t>
         </is>
       </c>
     </row>
@@ -5141,7 +5111,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mar-23 </t>
+          <t xml:space="preserve"> Aug-22 </t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5153,11 +5123,11 @@
         <v>45</v>
       </c>
       <c r="F134" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,200 </t>
+          <t xml:space="preserve"> 336 </t>
         </is>
       </c>
     </row>
@@ -5174,7 +5144,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Apr-23 </t>
+          <t xml:space="preserve"> Sep-22 </t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5186,11 +5156,11 @@
         <v>45</v>
       </c>
       <c r="F135" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,200 </t>
+          <t xml:space="preserve"> 1,056 </t>
         </is>
       </c>
     </row>
@@ -5207,7 +5177,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> May-23 </t>
+          <t xml:space="preserve"> Oct-22 </t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5219,11 +5189,11 @@
         <v>45</v>
       </c>
       <c r="F136" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,440 </t>
+          <t xml:space="preserve"> 696 </t>
         </is>
       </c>
     </row>
@@ -5240,7 +5210,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> June-23 </t>
+          <t xml:space="preserve"> Nov-22 </t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5252,11 +5222,11 @@
         <v>45</v>
       </c>
       <c r="F137" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,488 </t>
+          <t xml:space="preserve"> 360 </t>
         </is>
       </c>
     </row>
@@ -5273,7 +5243,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jul-23 </t>
+          <t xml:space="preserve"> Dec-22 </t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5285,11 +5255,11 @@
         <v>45</v>
       </c>
       <c r="F138" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,032 </t>
+          <t xml:space="preserve"> 864 </t>
         </is>
       </c>
     </row>
@@ -5306,7 +5276,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Aug-23 </t>
+          <t xml:space="preserve"> Jan-23 </t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5318,11 +5288,11 @@
         <v>45</v>
       </c>
       <c r="F139" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,344 </t>
+          <t xml:space="preserve"> 1,104 </t>
         </is>
       </c>
     </row>
@@ -5339,7 +5309,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sept-23 </t>
+          <t xml:space="preserve"> Feb-23 </t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5351,11 +5321,11 @@
         <v>45</v>
       </c>
       <c r="F140" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,440 </t>
+          <t xml:space="preserve"> 1,152 </t>
         </is>
       </c>
     </row>
@@ -5372,7 +5342,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Oct-23 </t>
+          <t xml:space="preserve"> Mar-23 </t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5384,11 +5354,11 @@
         <v>45</v>
       </c>
       <c r="F141" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,368 </t>
+          <t xml:space="preserve"> 1,200 </t>
         </is>
       </c>
     </row>
@@ -5405,7 +5375,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Nov-23 </t>
+          <t xml:space="preserve"> Apr-23 </t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5417,11 +5387,11 @@
         <v>45</v>
       </c>
       <c r="F142" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,512 </t>
+          <t xml:space="preserve"> 1,200 </t>
         </is>
       </c>
     </row>
@@ -5438,7 +5408,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dec-23 </t>
+          <t xml:space="preserve"> May-23 </t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5450,11 +5420,11 @@
         <v>45</v>
       </c>
       <c r="F143" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,200 </t>
+          <t xml:space="preserve"> 1,440 </t>
         </is>
       </c>
     </row>
@@ -5471,7 +5441,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jan-24 </t>
+          <t xml:space="preserve"> June-23 </t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5483,11 +5453,11 @@
         <v>45</v>
       </c>
       <c r="F144" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,560 </t>
+          <t xml:space="preserve"> 1,488 </t>
         </is>
       </c>
     </row>
@@ -5504,7 +5474,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feb-24 </t>
+          <t xml:space="preserve"> Jul-23 </t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5516,11 +5486,11 @@
         <v>45</v>
       </c>
       <c r="F145" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,368 </t>
+          <t xml:space="preserve"> 1,032 </t>
         </is>
       </c>
     </row>
@@ -5537,7 +5507,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mar-24 </t>
+          <t xml:space="preserve"> Aug-23 </t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5549,11 +5519,11 @@
         <v>45</v>
       </c>
       <c r="F146" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,776 </t>
+          <t xml:space="preserve"> 1,344 </t>
         </is>
       </c>
     </row>
@@ -5570,7 +5540,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Apr-24 </t>
+          <t xml:space="preserve"> Sept-23 </t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5582,11 +5552,11 @@
         <v>45</v>
       </c>
       <c r="F147" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,848 </t>
+          <t xml:space="preserve"> 1,440 </t>
         </is>
       </c>
     </row>
@@ -5603,7 +5573,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> May-24 </t>
+          <t xml:space="preserve"> Oct-23 </t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5612,14 +5582,14 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F148" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2,064 </t>
+          <t xml:space="preserve"> 1,368 </t>
         </is>
       </c>
     </row>
@@ -5636,7 +5606,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> June-24 </t>
+          <t xml:space="preserve"> Nov-23 </t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5645,14 +5615,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F149" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,152 </t>
+          <t xml:space="preserve"> 1,512 </t>
         </is>
       </c>
     </row>
@@ -5669,7 +5639,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> July-24 </t>
+          <t xml:space="preserve"> Dec-23 </t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5678,14 +5648,14 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F150" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,488 </t>
+          <t xml:space="preserve"> 1,200 </t>
         </is>
       </c>
     </row>
@@ -5702,7 +5672,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Aug-24 </t>
+          <t xml:space="preserve"> Jan-24 </t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5711,14 +5681,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F151" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2,160 </t>
+          <t xml:space="preserve"> 1,560 </t>
         </is>
       </c>
     </row>
@@ -5735,7 +5705,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sept-24 </t>
+          <t xml:space="preserve"> Feb-24 </t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5744,14 +5714,14 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F152" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,680 </t>
+          <t xml:space="preserve"> 1,368 </t>
         </is>
       </c>
     </row>
@@ -5768,7 +5738,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Oct-24 </t>
+          <t xml:space="preserve"> Mar-24 </t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5777,14 +5747,14 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F153" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,896 </t>
+          <t xml:space="preserve"> 1,776 </t>
         </is>
       </c>
     </row>
@@ -5801,7 +5771,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Nov-24 </t>
+          <t xml:space="preserve"> Apr-24 </t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5810,14 +5780,14 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F154" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,632 </t>
+          <t xml:space="preserve"> 1,848 </t>
         </is>
       </c>
     </row>
@@ -5834,7 +5804,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dec 2024 </t>
+          <t xml:space="preserve"> May-24 </t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5843,14 +5813,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F155" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2,928 </t>
+          <t xml:space="preserve"> 2,064 </t>
         </is>
       </c>
     </row>
@@ -5867,7 +5837,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jan-25 </t>
+          <t xml:space="preserve"> June-24 </t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5876,14 +5846,14 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F156" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,464 </t>
+          <t xml:space="preserve"> 1,152 </t>
         </is>
       </c>
     </row>
@@ -5900,7 +5870,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feb-25 </t>
+          <t xml:space="preserve"> July-24 </t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5909,14 +5879,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F157" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2,472 </t>
+          <t xml:space="preserve"> 1,488 </t>
         </is>
       </c>
     </row>
@@ -5933,7 +5903,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mar-25 </t>
+          <t xml:space="preserve"> Aug-24 </t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5942,14 +5912,14 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F158" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,344 </t>
+          <t xml:space="preserve"> 2,160 </t>
         </is>
       </c>
     </row>
@@ -5966,7 +5936,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Apr-25 </t>
+          <t xml:space="preserve"> Sept-24 </t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5975,14 +5945,14 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F159" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> -   </t>
+          <t xml:space="preserve"> 1,680 </t>
         </is>
       </c>
     </row>
@@ -5999,7 +5969,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> May 25 </t>
+          <t xml:space="preserve"> Oct-24 </t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -6008,14 +5978,14 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F160" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,920 </t>
+          <t xml:space="preserve"> 1,896 </t>
         </is>
       </c>
     </row>
@@ -6032,7 +6002,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> June-25 </t>
+          <t xml:space="preserve"> Nov-24 </t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -6041,14 +6011,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F161" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2,520 </t>
+          <t xml:space="preserve"> 1,632 </t>
         </is>
       </c>
     </row>
@@ -6065,7 +6035,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> July-25 </t>
+          <t xml:space="preserve"> Dec 2024 </t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -6074,14 +6044,14 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F162" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,032 </t>
+          <t xml:space="preserve"> 2,928 </t>
         </is>
       </c>
     </row>
@@ -6098,7 +6068,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Aug-25 </t>
+          <t xml:space="preserve"> Jan-25 </t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -6107,14 +6077,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F163" t="n">
         <v>14</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 48 </t>
+          <t xml:space="preserve"> 1,464 </t>
         </is>
       </c>
     </row>
@@ -6131,7 +6101,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sept-25 </t>
+          <t xml:space="preserve"> Feb-25 </t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -6140,14 +6110,14 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F164" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> -   </t>
+          <t xml:space="preserve"> 2,472 </t>
         </is>
       </c>
     </row>
@@ -6164,7 +6134,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Oct-25 </t>
+          <t xml:space="preserve"> Mar-25 </t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -6173,14 +6143,14 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F165" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> -   </t>
+          <t xml:space="preserve"> 1,344 </t>
         </is>
       </c>
     </row>
@@ -6197,7 +6167,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Nov-25 </t>
+          <t xml:space="preserve"> Apr-25 </t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -6206,14 +6176,14 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F166" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 576 </t>
+          <t xml:space="preserve"> -   </t>
         </is>
       </c>
     </row>
@@ -6230,7 +6200,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dec-25 </t>
+          <t xml:space="preserve"> May 25 </t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -6239,14 +6209,14 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F167" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 120 </t>
+          <t xml:space="preserve"> 1,920 </t>
         </is>
       </c>
     </row>
@@ -6263,7 +6233,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jan-26 </t>
+          <t xml:space="preserve"> June-25 </t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -6272,14 +6242,14 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F168" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 120 </t>
+          <t xml:space="preserve"> 2,520 </t>
         </is>
       </c>
     </row>
@@ -6296,7 +6266,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feb-26 </t>
+          <t xml:space="preserve"> July-25 </t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -6305,14 +6275,14 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F169" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 504 </t>
+          <t xml:space="preserve"> 1,032 </t>
         </is>
       </c>
     </row>
@@ -6329,7 +6299,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mar-26 </t>
+          <t xml:space="preserve"> Aug-25 </t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -6338,14 +6308,14 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F170" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 240 </t>
+          <t xml:space="preserve"> 48 </t>
         </is>
       </c>
     </row>
@@ -6362,7 +6332,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Apr-26 </t>
+          <t xml:space="preserve"> Sept-25 </t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -6371,14 +6341,14 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F171" t="n">
         <v>20</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 240 </t>
+          <t xml:space="preserve"> -   </t>
         </is>
       </c>
     </row>
@@ -6395,7 +6365,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> May-26 </t>
+          <t xml:space="preserve"> Oct-25 </t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -6404,14 +6374,14 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F172" t="n">
         <v>16</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 48 </t>
+          <t xml:space="preserve"> -   </t>
         </is>
       </c>
     </row>
@@ -6428,7 +6398,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> June-26 </t>
+          <t xml:space="preserve"> Nov-25 </t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -6437,14 +6407,14 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F173" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 168 </t>
+          <t xml:space="preserve"> 576 </t>
         </is>
       </c>
     </row>
@@ -6461,7 +6431,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jul-26 </t>
+          <t xml:space="preserve"> Dec-25 </t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -6470,14 +6440,14 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F174" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 144 </t>
+          <t xml:space="preserve"> 120 </t>
         </is>
       </c>
     </row>
@@ -6494,7 +6464,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Open Order 7-29-2026 </t>
+          <t xml:space="preserve"> Jan-26 </t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -6503,14 +6473,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F175" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 96 </t>
+          <t xml:space="preserve"> 120 </t>
         </is>
       </c>
     </row>
@@ -6527,7 +6497,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Released Order 7-29-2026 </t>
+          <t xml:space="preserve"> Feb-26 </t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -6536,14 +6506,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> -   </t>
+          <t xml:space="preserve"> 504 </t>
         </is>
       </c>
     </row>
@@ -6560,7 +6530,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Pending invoice-SAP 7-29-2026 </t>
+          <t xml:space="preserve"> Mar-26 </t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -6569,14 +6539,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F177" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 72 </t>
+          <t xml:space="preserve"> 240 </t>
         </is>
       </c>
     </row>
@@ -6593,7 +6563,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> July -26 </t>
+          <t xml:space="preserve"> Apr-26 </t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -6602,14 +6572,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F178" t="n">
         <v>20</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 312 </t>
+          <t xml:space="preserve"> 240 </t>
         </is>
       </c>
     </row>
@@ -6626,7 +6596,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> July'26- Forecast </t>
+          <t xml:space="preserve"> May-26 </t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -6635,14 +6605,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F179" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 250 </t>
+          <t xml:space="preserve"> 48 </t>
         </is>
       </c>
     </row>
@@ -6659,7 +6629,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Avg Jan'26 to June'26 </t>
+          <t xml:space="preserve"> June-26 </t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -6668,14 +6638,14 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F180" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 220 </t>
+          <t xml:space="preserve"> 168 </t>
         </is>
       </c>
     </row>
@@ -6692,7 +6662,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> % </t>
+          <t xml:space="preserve"> Jul-26 </t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -6704,11 +6674,11 @@
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t xml:space="preserve"> 144 </t>
         </is>
       </c>
     </row>
@@ -6725,7 +6695,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MTD-Target </t>
+          <t xml:space="preserve"> Open Order 7-29-2026 </t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -6734,21 +6704,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 220 </t>
+          <t xml:space="preserve"> 96 </t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Headers.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6758,7 +6728,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Sales Order No.</t>
+          <t xml:space="preserve"> Released Order 7-29-2026 </t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -6770,18 +6740,18 @@
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Orderbook</t>
+          <t xml:space="preserve"> -   </t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Headers.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6791,7 +6761,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Item No.</t>
+          <t xml:space="preserve"> Pending invoice-SAP 7-29-2026 </t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -6800,21 +6770,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Item No.</t>
+          <t xml:space="preserve"> 72 </t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Headers.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6824,7 +6794,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Matl.Code</t>
+          <t xml:space="preserve"> July -26 </t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -6833,21 +6803,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lookup</t>
+          <t xml:space="preserve"> 312 </t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Headers.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6857,7 +6827,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>NDC Code</t>
+          <t xml:space="preserve"> July'26- Forecast </t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -6866,22 +6836,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Matl._x000d_
-Code</t>
+          <t xml:space="preserve"> 250 </t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Headers.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6891,7 +6860,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Material Description</t>
+          <t xml:space="preserve"> Avg Jan'26 to June'26 </t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -6900,21 +6869,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>NDC Code</t>
+          <t xml:space="preserve"> 220 </t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Headers.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6924,7 +6893,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Total Stock In-hand</t>
+          <t xml:space="preserve"> % </t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -6933,21 +6902,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Material Description</t>
+          <t>65%</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Headers.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6957,7 +6926,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>PackSize(MOQ)</t>
+          <t xml:space="preserve"> MTD-Target </t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -6966,1005 +6935,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Total Stock _x000d_
-In-hand</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Sales Order Qty</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E190" t="n">
-        <v>2</v>
-      </c>
-      <c r="F190" t="n">
-        <v>2</v>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>UPS Inventory</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Sales Qty MTD</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E191" t="n">
-        <v>2</v>
-      </c>
-      <c r="F191" t="n">
-        <v>2</v>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>Pack Size (MOQ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Forecast Qty</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E192" t="n">
-        <v>2</v>
-      </c>
-      <c r="F192" t="n">
-        <v>2</v>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>Sales Order Qty</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Sold-to party</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E193" t="n">
-        <v>2</v>
-      </c>
-      <c r="F193" t="n">
-        <v>2</v>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>Sales Qty MTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Sold-to party Name</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E194" t="n">
-        <v>2</v>
-      </c>
-      <c r="F194" t="n">
-        <v>2</v>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>Forecast Qty</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>S.O. Type</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E195" t="n">
-        <v>2</v>
-      </c>
-      <c r="F195" t="n">
-        <v>2</v>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Sold-to party</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Unit Price</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E196" t="n">
-        <v>2</v>
-      </c>
-      <c r="F196" t="n">
-        <v>2</v>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>Sold-to party Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Sales Value (FC)</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E197" t="n">
-        <v>2</v>
-      </c>
-      <c r="F197" t="n">
-        <v>2</v>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>WAC/BG price in EDI</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E198" t="n">
-        <v>2</v>
-      </c>
-      <c r="F198" t="n">
-        <v>2</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>S.O. Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>PO number</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E199" t="n">
-        <v>3</v>
-      </c>
-      <c r="F199" t="n">
-        <v>1</v>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Unit Price </t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>PO date</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E200" t="n">
-        <v>3</v>
-      </c>
-      <c r="F200" t="n">
-        <v>1</v>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Sales Value (FC) </t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Ship-to party</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E201" t="n">
-        <v>3</v>
-      </c>
-      <c r="F201" t="n">
-        <v>1</v>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>WAC/BG price in EDI</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Ship-to party Name</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E202" t="n">
-        <v>3</v>
-      </c>
-      <c r="F202" t="n">
-        <v>1</v>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>PO Number</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Street</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E203" t="n">
-        <v>3</v>
-      </c>
-      <c r="F203" t="n">
-        <v>1</v>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>PO Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E204" t="n">
-        <v>3</v>
-      </c>
-      <c r="F204" t="n">
-        <v>1</v>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Ship-to party</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E205" t="n">
-        <v>3</v>
-      </c>
-      <c r="F205" t="n">
-        <v>1</v>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>Ship-to party Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Postal Code</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E206" t="n">
-        <v>3</v>
-      </c>
-      <c r="F206" t="n">
-        <v>1</v>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>Street</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E207" t="n">
-        <v>3</v>
-      </c>
-      <c r="F207" t="n">
-        <v>1</v>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Reas. Rej.</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E208" t="n">
-        <v>3</v>
-      </c>
-      <c r="F208" t="n">
-        <v>1</v>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Reason for Rejection</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E209" t="n">
-        <v>3</v>
-      </c>
-      <c r="F209" t="n">
-        <v>1</v>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>Postal Code</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Material Blk</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E210" t="n">
-        <v>3</v>
-      </c>
-      <c r="F210" t="n">
-        <v>1</v>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Floor limit Blk</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E211" t="n">
-        <v>3</v>
-      </c>
-      <c r="F211" t="n">
-        <v>1</v>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>Reas. Rej.</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Multiple of MOQ Blk</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E212" t="n">
-        <v>3</v>
-      </c>
-      <c r="F212" t="n">
-        <v>1</v>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Reason for Rejection</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Expected Price Blk</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E213" t="n">
-        <v>3</v>
-      </c>
-      <c r="F213" t="n">
-        <v>1</v>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Material Blk</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>DEA Number (Customer Master)</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E214" t="n">
-        <v>3</v>
-      </c>
-      <c r="F214" t="n">
-        <v>1</v>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>Floor limit Blk</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Req. Delivery Date</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E215" t="n">
-        <v>3</v>
-      </c>
-      <c r="F215" t="n">
-        <v>1</v>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>Multiple of MOQ Blk</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>SOM Indc.</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E216" t="n">
-        <v>3</v>
-      </c>
-      <c r="F216" t="n">
-        <v>1</v>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>Expected Price Blk</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Unnamed: 34</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E217" t="n">
-        <v>3</v>
-      </c>
-      <c r="F217" t="n">
-        <v>1</v>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>DEA Number (Customer Master)</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Unnamed: 35</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E218" t="n">
-        <v>3</v>
-      </c>
-      <c r="F218" t="n">
-        <v>1</v>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>Req. Delivery Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Headers.xlsx</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Unnamed: 36</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E219" t="n">
-        <v>3</v>
-      </c>
-      <c r="F219" t="n">
-        <v>1</v>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>SOM Indc.</t>
+          <t xml:space="preserve"> 220 </t>
         </is>
       </c>
     </row>
